--- a/artfynd/A 48909-2023 artfynd.xlsx
+++ b/artfynd/A 48909-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 48909-2023 artfynd.xlsx
+++ b/artfynd/A 48909-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,32 +675,27 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>81138975</v>
+        <v>106978066</v>
       </c>
       <c r="B2" t="n">
-        <v>56538</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>56925</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103020</v>
+        <v>100045</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Sångsvan</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Poecile palustris</t>
+          <t>Cygnus cygnus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -709,20 +704,16 @@
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Stjärnarpsskogen, Kohagadammen, Hl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>376219.9057044232</v>
+        <v>376234</v>
       </c>
       <c r="R2" t="n">
-        <v>6279150.217384581</v>
+        <v>6279288</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -749,22 +740,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2019-12-10</t>
+          <t>2023-02-23</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2019-12-10</t>
+          <t>2023-02-23</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -791,37 +782,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>85147264</v>
+        <v>81730613</v>
       </c>
       <c r="B3" t="n">
-        <v>56632</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103012</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Grönsångare</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phylloscopus sibilatrix</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Bechstein, 1793)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -829,21 +815,16 @@
           <t>1</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Stjärnarpsskogen, Kohagadammen, Hl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>376238.1416778454</v>
+        <v>376227</v>
       </c>
       <c r="R3" t="n">
-        <v>6279301.528917734</v>
+        <v>6279218</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -870,22 +851,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2020-05-05</t>
+          <t>2020-01-13</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2020-05-05</t>
+          <t>2020-01-13</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -912,19 +893,14 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119693342</v>
+        <v>96723328</v>
       </c>
       <c r="B4" t="n">
-        <v>57326</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -952,10 +928,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>376220</v>
+        <v>376219</v>
       </c>
       <c r="R4" t="n">
-        <v>6279162</v>
+        <v>6279256</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -982,22 +958,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-09-10</t>
+          <t>2021-09-21</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-09-10</t>
+          <t>2021-09-21</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1021,6 +997,1547 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>106978065</v>
+      </c>
+      <c r="B5" t="n">
+        <v>57950</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Stjärnarpsskogen, Kohagadammen, Hl</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>376234</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6279290</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Halland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Halmstad</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Halland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Eldsberga</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2023-02-23</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>09:51</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2023-02-23</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>09:51</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Börje Andersson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Börje Andersson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>119693342</v>
+      </c>
+      <c r="B6" t="n">
+        <v>57950</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Stjärnarpsskogen, Kohagadammen, Hl</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>376220</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6279162</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Halland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Halmstad</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Halland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Eldsberga</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2024-09-10</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>15:17</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2024-09-10</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>15:17</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Börje Andersson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Börje Andersson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>123937260</v>
+      </c>
+      <c r="B7" t="n">
+        <v>57950</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Stjärnarpsskogen, Kohagadammen, Hl</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>376224</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6279244</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Halland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Halmstad</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Halland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Eldsberga</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-04-05</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>10:01</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-04-05</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>10:01</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Trummande</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Börje Andersson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Börje Andersson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>111224636</v>
+      </c>
+      <c r="B8" t="n">
+        <v>58497</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>102990</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Järnsparv</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Prunella modularis</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Stjärnarpsskogen, Kohagadammen, Hl</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>376229</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6279312</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Halland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Halmstad</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Halland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Eldsberga</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2023-04-28</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>10:39</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2023-04-28</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>10:39</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Börje Andersson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Börje Andersson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>85147264</v>
+      </c>
+      <c r="B9" t="n">
+        <v>58238</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>103012</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Grönsångare</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Phylloscopus sibilatrix</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Bechstein, 1793)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Stjärnarpsskogen, Kohagadammen, Hl</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>376238</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6279302</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Halland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Halmstad</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Halland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Eldsberga</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2020-05-05</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>10:06</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2020-05-05</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>10:06</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Börje Andersson</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Börje Andersson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>81138978</v>
+      </c>
+      <c r="B10" t="n">
+        <v>58327</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Stjärnarpsskogen, Kohagadammen, Hl</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>376222</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6279151</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Halland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Halmstad</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Halland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Eldsberga</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2019-12-10</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>10:27</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2019-12-10</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>10:27</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Börje Andersson</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Börje Andersson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>81629194</v>
+      </c>
+      <c r="B11" t="n">
+        <v>58327</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Stjärnarpsskogen, Kohagadammen, Hl</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>376216</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6279084</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Halland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Halmstad</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Halland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Eldsberga</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2020-01-05</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>09:15</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2020-01-05</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>09:15</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Börje Andersson</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Börje Andersson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>96723329</v>
+      </c>
+      <c r="B12" t="n">
+        <v>58327</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Stjärnarpsskogen, Kohagadammen, Hl</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>376222</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6279253</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Halland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Halmstad</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Halland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Eldsberga</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2021-09-21</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2021-09-21</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Börje Andersson</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Börje Andersson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>104679227</v>
+      </c>
+      <c r="B13" t="n">
+        <v>58327</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Stjärnarpsskogen, Kohagadammen, Hl</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>376229</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6279372</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Halland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Halmstad</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Halland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Eldsberga</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2022-11-15</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2022-11-15</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Börje Andersson</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Börje Andersson</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>104914252</v>
+      </c>
+      <c r="B14" t="n">
+        <v>58327</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Stjärnarpsskogen, Kohagadammen, Hl</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>376245</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6279361</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Halland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Halmstad</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Halland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Eldsberga</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2022-11-25</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>10:50</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2022-11-25</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>10:50</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Börje Andersson</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Börje Andersson</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>105492284</v>
+      </c>
+      <c r="B15" t="n">
+        <v>58327</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Stjärnarpsskogen, Kohagadammen, Hl</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>376218</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6279094</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Halland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Halmstad</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Halland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Eldsberga</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2022-12-11</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>11:46</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2022-12-11</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>11:46</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Börje Andersson</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Börje Andersson</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>112216975</v>
+      </c>
+      <c r="B16" t="n">
+        <v>58327</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Stjärnarpsskogen, Kohagadammen, Hl</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>376216</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6279142</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Halland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Halmstad</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Halland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Eldsberga</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2023-08-14</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>10:53</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2023-08-14</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>10:53</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Börje Andersson</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Börje Andersson</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>81138975</v>
+      </c>
+      <c r="B17" t="n">
+        <v>58112</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>103020</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Entita</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Poecile palustris</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Stjärnarpsskogen, Kohagadammen, Hl</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>376220</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6279150</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Halland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Halmstad</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Halland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Eldsberga</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2019-12-10</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>10:27</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2019-12-10</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>10:27</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Börje Andersson</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Börje Andersson</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>113893516</v>
+      </c>
+      <c r="B18" t="n">
+        <v>58112</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>103020</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Entita</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Poecile palustris</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Stjärnarpsskogen, Kohagadammen, Hl</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>376215</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6279078</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Halland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Halmstad</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Halland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Eldsberga</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2024-01-04</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2024-01-04</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Börje Andersson</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Börje Andersson</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 48909-2023 artfynd.xlsx
+++ b/artfynd/A 48909-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY18"/>
+  <dimension ref="A1:AZ18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106978066</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -890,6 +900,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/81730613</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -997,6 +1012,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96723328</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1104,6 +1124,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106978065</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1211,6 +1236,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119693342</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1323,6 +1353,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123937260</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1435,6 +1470,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111224636</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1551,6 +1591,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/85147264</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1662,6 +1707,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/81138978</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1777,6 +1827,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/81629194</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1884,6 +1939,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96723329</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1991,6 +2051,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104679227</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2098,6 +2163,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104914252</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2209,6 +2279,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105492284</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2316,6 +2391,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112216975</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2427,6 +2507,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/81138975</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2538,8 +2623,32 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113893516</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>